--- a/artfynd/A 46558-2023 artfynd.xlsx
+++ b/artfynd/A 46558-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46558-2023 artfynd.xlsx
+++ b/artfynd/A 46558-2023 artfynd.xlsx
@@ -9002,10 +9002,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117853211</v>
+        <v>117853179</v>
       </c>
       <c r="B83" t="n">
-        <v>91772</v>
+        <v>91962</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9014,25 +9014,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>822530</v>
+        <v>822868</v>
       </c>
       <c r="R83" t="n">
-        <v>7365892</v>
+        <v>7365856</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9104,10 +9104,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117853192</v>
+        <v>117853169</v>
       </c>
       <c r="B84" t="n">
-        <v>56491</v>
+        <v>57287</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9120,16 +9120,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9138,16 +9138,21 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>822753</v>
+        <v>822940</v>
       </c>
       <c r="R84" t="n">
-        <v>7365626</v>
+        <v>7365714</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9206,10 +9211,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117853179</v>
+        <v>117853211</v>
       </c>
       <c r="B85" t="n">
-        <v>91962</v>
+        <v>91772</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9218,25 +9223,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9246,10 +9251,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>822868</v>
+        <v>822530</v>
       </c>
       <c r="R85" t="n">
-        <v>7365856</v>
+        <v>7365892</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9418,10 +9423,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117853169</v>
+        <v>117853185</v>
       </c>
       <c r="B87" t="n">
-        <v>57287</v>
+        <v>78217</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9434,39 +9439,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>822940</v>
+        <v>822091</v>
       </c>
       <c r="R87" t="n">
-        <v>7365714</v>
+        <v>7366269</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9525,10 +9525,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117853185</v>
+        <v>117853192</v>
       </c>
       <c r="B88" t="n">
-        <v>78217</v>
+        <v>56491</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9541,21 +9541,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>102612</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9565,10 +9565,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>822091</v>
+        <v>822753</v>
       </c>
       <c r="R88" t="n">
-        <v>7366269</v>
+        <v>7365626</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>

--- a/artfynd/A 46558-2023 artfynd.xlsx
+++ b/artfynd/A 46558-2023 artfynd.xlsx
@@ -7234,10 +7234,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117853224</v>
+        <v>117853172</v>
       </c>
       <c r="B66" t="n">
-        <v>78125</v>
+        <v>56499</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7246,38 +7246,46 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>822990</v>
+        <v>823088</v>
       </c>
       <c r="R66" t="n">
-        <v>7365573</v>
+        <v>7365374</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7336,10 +7344,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117853193</v>
+        <v>117853189</v>
       </c>
       <c r="B67" t="n">
-        <v>56491</v>
+        <v>78216</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7352,21 +7360,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7376,10 +7384,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>822864</v>
+        <v>823206</v>
       </c>
       <c r="R67" t="n">
-        <v>7365846</v>
+        <v>7365372</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7438,10 +7446,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117853189</v>
+        <v>117853213</v>
       </c>
       <c r="B68" t="n">
-        <v>78216</v>
+        <v>91772</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7450,25 +7458,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7478,10 +7486,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>823206</v>
+        <v>823075</v>
       </c>
       <c r="R68" t="n">
-        <v>7365372</v>
+        <v>7365464</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7540,10 +7548,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117853165</v>
+        <v>117853191</v>
       </c>
       <c r="B69" t="n">
-        <v>79069</v>
+        <v>56491</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7556,21 +7564,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229821</v>
+        <v>102612</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7580,10 +7588,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>822653</v>
+        <v>822405</v>
       </c>
       <c r="R69" t="n">
-        <v>7365804</v>
+        <v>7365885</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7642,10 +7650,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117853209</v>
+        <v>117853198</v>
       </c>
       <c r="B70" t="n">
-        <v>91772</v>
+        <v>90648</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7654,25 +7662,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7682,10 +7690,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>822437</v>
+        <v>823072</v>
       </c>
       <c r="R70" t="n">
-        <v>7365878</v>
+        <v>7365396</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7744,10 +7752,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117853219</v>
+        <v>117853205</v>
       </c>
       <c r="B71" t="n">
-        <v>91772</v>
+        <v>78480</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7756,25 +7764,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7784,10 +7792,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>822120</v>
+        <v>823085</v>
       </c>
       <c r="R71" t="n">
-        <v>7366257</v>
+        <v>7365474</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7846,10 +7854,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117853207</v>
+        <v>117853181</v>
       </c>
       <c r="B72" t="n">
-        <v>90743</v>
+        <v>91962</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7858,25 +7866,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7886,10 +7894,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>823183</v>
+        <v>822952</v>
       </c>
       <c r="R72" t="n">
-        <v>7365421</v>
+        <v>7365646</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -7948,10 +7956,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117853168</v>
+        <v>117853171</v>
       </c>
       <c r="B73" t="n">
-        <v>57287</v>
+        <v>56499</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7960,43 +7968,46 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>822926</v>
+        <v>822957</v>
       </c>
       <c r="R73" t="n">
-        <v>7365734</v>
+        <v>7365588</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8055,10 +8066,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117853167</v>
+        <v>117853209</v>
       </c>
       <c r="B74" t="n">
-        <v>57287</v>
+        <v>91772</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8067,43 +8078,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>822380</v>
+        <v>822437</v>
       </c>
       <c r="R74" t="n">
-        <v>7365964</v>
+        <v>7365878</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8162,10 +8168,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117853213</v>
+        <v>117853165</v>
       </c>
       <c r="B75" t="n">
-        <v>91772</v>
+        <v>79069</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8174,25 +8180,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8202,10 +8208,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>823075</v>
+        <v>822653</v>
       </c>
       <c r="R75" t="n">
-        <v>7365464</v>
+        <v>7365804</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8264,10 +8270,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117853214</v>
+        <v>117853197</v>
       </c>
       <c r="B76" t="n">
-        <v>91772</v>
+        <v>90648</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8276,25 +8282,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8304,10 +8310,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>823096</v>
+        <v>822876</v>
       </c>
       <c r="R76" t="n">
-        <v>7365376</v>
+        <v>7365854</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8366,10 +8372,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117853170</v>
+        <v>117853177</v>
       </c>
       <c r="B77" t="n">
-        <v>56499</v>
+        <v>56491</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8378,46 +8384,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>822667</v>
+        <v>822670</v>
       </c>
       <c r="R77" t="n">
-        <v>7365784</v>
+        <v>7365699</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8476,10 +8474,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117853172</v>
+        <v>117853167</v>
       </c>
       <c r="B78" t="n">
-        <v>56499</v>
+        <v>57287</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8488,46 +8486,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>823088</v>
+        <v>822380</v>
       </c>
       <c r="R78" t="n">
-        <v>7365374</v>
+        <v>7365964</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8586,10 +8581,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117853216</v>
+        <v>117853184</v>
       </c>
       <c r="B79" t="n">
-        <v>91772</v>
+        <v>78217</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8598,25 +8593,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8626,10 +8621,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>823228</v>
+        <v>823212</v>
       </c>
       <c r="R79" t="n">
-        <v>7365303</v>
+        <v>7365304</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8688,10 +8683,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117853221</v>
+        <v>117853178</v>
       </c>
       <c r="B80" t="n">
-        <v>91772</v>
+        <v>79589</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8704,21 +8699,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8728,10 +8723,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>822747</v>
+        <v>823075</v>
       </c>
       <c r="R80" t="n">
-        <v>7365610</v>
+        <v>7365404</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8790,10 +8785,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117853180</v>
+        <v>117853170</v>
       </c>
       <c r="B81" t="n">
-        <v>91962</v>
+        <v>56499</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8802,38 +8797,46 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>822936</v>
+        <v>822667</v>
       </c>
       <c r="R81" t="n">
-        <v>7365718</v>
+        <v>7365784</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8892,10 +8895,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117853173</v>
+        <v>117853200</v>
       </c>
       <c r="B82" t="n">
-        <v>56499</v>
+        <v>90648</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8904,46 +8907,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>822971</v>
+        <v>823068</v>
       </c>
       <c r="R82" t="n">
-        <v>7365573</v>
+        <v>7365393</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9002,10 +8997,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117853179</v>
+        <v>117853176</v>
       </c>
       <c r="B83" t="n">
-        <v>91962</v>
+        <v>91815</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9018,21 +9013,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2079</v>
+        <v>5448</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9042,10 +9037,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>822868</v>
+        <v>823178</v>
       </c>
       <c r="R83" t="n">
-        <v>7365856</v>
+        <v>7365412</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9104,10 +9099,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117853169</v>
+        <v>117853192</v>
       </c>
       <c r="B84" t="n">
-        <v>57287</v>
+        <v>56491</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9120,16 +9115,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9138,21 +9133,16 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>822940</v>
+        <v>822753</v>
       </c>
       <c r="R84" t="n">
-        <v>7365714</v>
+        <v>7365626</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9211,10 +9201,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117853211</v>
+        <v>117853169</v>
       </c>
       <c r="B85" t="n">
-        <v>91772</v>
+        <v>57287</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9223,38 +9213,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>822530</v>
+        <v>822940</v>
       </c>
       <c r="R85" t="n">
-        <v>7365892</v>
+        <v>7365714</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9313,10 +9308,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117853174</v>
+        <v>117853219</v>
       </c>
       <c r="B86" t="n">
-        <v>56499</v>
+        <v>91772</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9329,42 +9324,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>822658</v>
+        <v>822120</v>
       </c>
       <c r="R86" t="n">
-        <v>7365727</v>
+        <v>7366257</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9423,10 +9410,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117853185</v>
+        <v>117853193</v>
       </c>
       <c r="B87" t="n">
-        <v>78217</v>
+        <v>56491</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9439,21 +9426,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>102612</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9463,10 +9450,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>822091</v>
+        <v>822864</v>
       </c>
       <c r="R87" t="n">
-        <v>7366269</v>
+        <v>7365846</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9525,10 +9512,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117853192</v>
+        <v>117853180</v>
       </c>
       <c r="B88" t="n">
-        <v>56491</v>
+        <v>91962</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9541,21 +9528,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102612</v>
+        <v>2079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9565,10 +9552,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>822753</v>
+        <v>822936</v>
       </c>
       <c r="R88" t="n">
-        <v>7365626</v>
+        <v>7365718</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9627,10 +9614,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117853218</v>
+        <v>117853183</v>
       </c>
       <c r="B89" t="n">
-        <v>91772</v>
+        <v>91962</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9639,25 +9626,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9670,7 +9657,7 @@
         <v>823109</v>
       </c>
       <c r="R89" t="n">
-        <v>7365360</v>
+        <v>7365464</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9729,10 +9716,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117853175</v>
+        <v>117853214</v>
       </c>
       <c r="B90" t="n">
-        <v>57440</v>
+        <v>91772</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9741,46 +9728,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>822405</v>
+        <v>823096</v>
       </c>
       <c r="R90" t="n">
-        <v>7365900</v>
+        <v>7365376</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -9839,10 +9818,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117853200</v>
+        <v>117853166</v>
       </c>
       <c r="B91" t="n">
-        <v>90648</v>
+        <v>57287</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9851,38 +9830,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>823068</v>
+        <v>822278</v>
       </c>
       <c r="R91" t="n">
-        <v>7365393</v>
+        <v>7366097</v>
       </c>
       <c r="S91" t="n">
         <v>20</v>
@@ -9941,10 +9925,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117853182</v>
+        <v>117853203</v>
       </c>
       <c r="B92" t="n">
-        <v>91962</v>
+        <v>78480</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9957,21 +9941,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9981,10 +9965,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>823221</v>
+        <v>822790</v>
       </c>
       <c r="R92" t="n">
-        <v>7365370</v>
+        <v>7365917</v>
       </c>
       <c r="S92" t="n">
         <v>20</v>
@@ -10043,10 +10027,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117853176</v>
+        <v>117853173</v>
       </c>
       <c r="B93" t="n">
-        <v>91815</v>
+        <v>56499</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10055,38 +10039,46 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5448</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>823178</v>
+        <v>822971</v>
       </c>
       <c r="R93" t="n">
-        <v>7365412</v>
+        <v>7365573</v>
       </c>
       <c r="S93" t="n">
         <v>20</v>
@@ -10145,10 +10137,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117853178</v>
+        <v>117853188</v>
       </c>
       <c r="B94" t="n">
-        <v>79589</v>
+        <v>78216</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10157,25 +10149,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6461</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10185,10 +10177,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>823075</v>
+        <v>822917</v>
       </c>
       <c r="R94" t="n">
-        <v>7365404</v>
+        <v>7365810</v>
       </c>
       <c r="S94" t="n">
         <v>20</v>
@@ -10247,10 +10239,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117853171</v>
+        <v>117853185</v>
       </c>
       <c r="B95" t="n">
-        <v>56499</v>
+        <v>78217</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10259,46 +10251,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>822957</v>
+        <v>822091</v>
       </c>
       <c r="R95" t="n">
-        <v>7365588</v>
+        <v>7366269</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -10357,10 +10341,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117853166</v>
+        <v>117853164</v>
       </c>
       <c r="B96" t="n">
-        <v>57287</v>
+        <v>79069</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10373,39 +10357,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>822278</v>
+        <v>823236</v>
       </c>
       <c r="R96" t="n">
-        <v>7366097</v>
+        <v>7365333</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -10464,10 +10443,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117853190</v>
+        <v>117853179</v>
       </c>
       <c r="B97" t="n">
-        <v>78216</v>
+        <v>91962</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10480,21 +10459,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10504,10 +10483,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>822973</v>
+        <v>822868</v>
       </c>
       <c r="R97" t="n">
-        <v>7365570</v>
+        <v>7365856</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10566,10 +10545,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117853164</v>
+        <v>117853216</v>
       </c>
       <c r="B98" t="n">
-        <v>79069</v>
+        <v>91772</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10578,25 +10557,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10606,10 +10585,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>823236</v>
+        <v>823228</v>
       </c>
       <c r="R98" t="n">
-        <v>7365333</v>
+        <v>7365303</v>
       </c>
       <c r="S98" t="n">
         <v>20</v>
@@ -10668,10 +10647,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117853194</v>
+        <v>117853163</v>
       </c>
       <c r="B99" t="n">
-        <v>91962</v>
+        <v>79098</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10684,21 +10663,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10708,10 +10687,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>822973</v>
+        <v>822961</v>
       </c>
       <c r="R99" t="n">
-        <v>7365566</v>
+        <v>7365570</v>
       </c>
       <c r="S99" t="n">
         <v>20</v>
@@ -10770,10 +10749,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117853197</v>
+        <v>117853161</v>
       </c>
       <c r="B100" t="n">
-        <v>90648</v>
+        <v>79098</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10782,25 +10761,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10810,10 +10789,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>822876</v>
+        <v>822791</v>
       </c>
       <c r="R100" t="n">
-        <v>7365854</v>
+        <v>7365910</v>
       </c>
       <c r="S100" t="n">
         <v>20</v>
@@ -10872,10 +10851,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>117853188</v>
+        <v>117853224</v>
       </c>
       <c r="B101" t="n">
-        <v>78216</v>
+        <v>78125</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10888,21 +10867,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10912,10 +10891,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>822917</v>
+        <v>822990</v>
       </c>
       <c r="R101" t="n">
-        <v>7365810</v>
+        <v>7365573</v>
       </c>
       <c r="S101" t="n">
         <v>20</v>
@@ -10974,10 +10953,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117853198</v>
+        <v>117853182</v>
       </c>
       <c r="B102" t="n">
-        <v>90648</v>
+        <v>91962</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10986,25 +10965,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11014,10 +10993,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>823072</v>
+        <v>823221</v>
       </c>
       <c r="R102" t="n">
-        <v>7365396</v>
+        <v>7365370</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -11076,10 +11055,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117853184</v>
+        <v>117853218</v>
       </c>
       <c r="B103" t="n">
-        <v>78217</v>
+        <v>91772</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11088,25 +11067,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11116,10 +11095,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>823212</v>
+        <v>823109</v>
       </c>
       <c r="R103" t="n">
-        <v>7365304</v>
+        <v>7365360</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -11178,10 +11157,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>117853161</v>
+        <v>117853211</v>
       </c>
       <c r="B104" t="n">
-        <v>79098</v>
+        <v>91772</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11190,25 +11169,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11218,10 +11197,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>822791</v>
+        <v>822530</v>
       </c>
       <c r="R104" t="n">
-        <v>7365910</v>
+        <v>7365892</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -11280,10 +11259,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>117853177</v>
+        <v>117853194</v>
       </c>
       <c r="B105" t="n">
-        <v>56491</v>
+        <v>91962</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11296,21 +11275,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>102612</v>
+        <v>2079</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11320,10 +11299,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>822670</v>
+        <v>822973</v>
       </c>
       <c r="R105" t="n">
-        <v>7365699</v>
+        <v>7365566</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -11382,10 +11361,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>117853181</v>
+        <v>117853174</v>
       </c>
       <c r="B106" t="n">
-        <v>91962</v>
+        <v>56499</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11394,38 +11373,46 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>822952</v>
+        <v>822658</v>
       </c>
       <c r="R106" t="n">
-        <v>7365646</v>
+        <v>7365727</v>
       </c>
       <c r="S106" t="n">
         <v>20</v>
@@ -11484,10 +11471,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>117853191</v>
+        <v>117853207</v>
       </c>
       <c r="B107" t="n">
-        <v>56491</v>
+        <v>90743</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11496,25 +11483,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>102612</v>
+        <v>65</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11524,10 +11511,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>822405</v>
+        <v>823183</v>
       </c>
       <c r="R107" t="n">
-        <v>7365885</v>
+        <v>7365421</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -11586,10 +11573,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>117853203</v>
+        <v>117853175</v>
       </c>
       <c r="B108" t="n">
-        <v>78480</v>
+        <v>57440</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11602,34 +11589,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>822790</v>
+        <v>822405</v>
       </c>
       <c r="R108" t="n">
-        <v>7365917</v>
+        <v>7365900</v>
       </c>
       <c r="S108" t="n">
         <v>20</v>
@@ -11688,10 +11683,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>117853202</v>
+        <v>117853168</v>
       </c>
       <c r="B109" t="n">
-        <v>90648</v>
+        <v>57287</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11700,38 +11695,43 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>823210</v>
+        <v>822926</v>
       </c>
       <c r="R109" t="n">
-        <v>7365304</v>
+        <v>7365734</v>
       </c>
       <c r="S109" t="n">
         <v>20</v>
@@ -11790,10 +11790,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>117853205</v>
+        <v>117853202</v>
       </c>
       <c r="B110" t="n">
-        <v>78480</v>
+        <v>90648</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11802,25 +11802,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11830,10 +11830,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>823085</v>
+        <v>823210</v>
       </c>
       <c r="R110" t="n">
-        <v>7365474</v>
+        <v>7365304</v>
       </c>
       <c r="S110" t="n">
         <v>20</v>
@@ -11892,10 +11892,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>117853163</v>
+        <v>117853221</v>
       </c>
       <c r="B111" t="n">
-        <v>79098</v>
+        <v>91772</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11904,25 +11904,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11932,10 +11932,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>822961</v>
+        <v>822747</v>
       </c>
       <c r="R111" t="n">
-        <v>7365570</v>
+        <v>7365610</v>
       </c>
       <c r="S111" t="n">
         <v>20</v>
@@ -11994,10 +11994,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>117853183</v>
+        <v>117853190</v>
       </c>
       <c r="B112" t="n">
-        <v>91962</v>
+        <v>78216</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12010,21 +12010,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12034,10 +12034,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>823109</v>
+        <v>822973</v>
       </c>
       <c r="R112" t="n">
-        <v>7365464</v>
+        <v>7365570</v>
       </c>
       <c r="S112" t="n">
         <v>20</v>

--- a/artfynd/A 46558-2023 artfynd.xlsx
+++ b/artfynd/A 46558-2023 artfynd.xlsx
@@ -7234,10 +7234,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117853172</v>
+        <v>117853180</v>
       </c>
       <c r="B66" t="n">
-        <v>56499</v>
+        <v>91964</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7246,46 +7246,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>823088</v>
+        <v>822936</v>
       </c>
       <c r="R66" t="n">
-        <v>7365374</v>
+        <v>7365718</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7344,10 +7336,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117853189</v>
+        <v>117853221</v>
       </c>
       <c r="B67" t="n">
-        <v>78216</v>
+        <v>91774</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7356,25 +7348,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7384,10 +7376,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>823206</v>
+        <v>822747</v>
       </c>
       <c r="R67" t="n">
-        <v>7365372</v>
+        <v>7365610</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7446,10 +7438,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117853213</v>
+        <v>117853173</v>
       </c>
       <c r="B68" t="n">
-        <v>91772</v>
+        <v>56500</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7462,34 +7454,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>823075</v>
+        <v>822971</v>
       </c>
       <c r="R68" t="n">
-        <v>7365464</v>
+        <v>7365573</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7548,10 +7548,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117853191</v>
+        <v>117853178</v>
       </c>
       <c r="B69" t="n">
-        <v>56491</v>
+        <v>79591</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7560,25 +7560,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>822405</v>
+        <v>823075</v>
       </c>
       <c r="R69" t="n">
-        <v>7365885</v>
+        <v>7365404</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7650,10 +7650,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117853198</v>
+        <v>117853203</v>
       </c>
       <c r="B70" t="n">
-        <v>90648</v>
+        <v>78482</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7662,25 +7662,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>823072</v>
+        <v>822790</v>
       </c>
       <c r="R70" t="n">
-        <v>7365396</v>
+        <v>7365917</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7752,10 +7752,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117853205</v>
+        <v>117853182</v>
       </c>
       <c r="B71" t="n">
-        <v>78480</v>
+        <v>91964</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7768,21 +7768,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7792,10 +7792,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>823085</v>
+        <v>823221</v>
       </c>
       <c r="R71" t="n">
-        <v>7365474</v>
+        <v>7365370</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7854,10 +7854,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117853181</v>
+        <v>117853176</v>
       </c>
       <c r="B72" t="n">
-        <v>91962</v>
+        <v>91817</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7870,21 +7870,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2079</v>
+        <v>5448</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>822952</v>
+        <v>823178</v>
       </c>
       <c r="R72" t="n">
-        <v>7365646</v>
+        <v>7365412</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -7956,10 +7956,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117853171</v>
+        <v>117853172</v>
       </c>
       <c r="B73" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>822957</v>
+        <v>823088</v>
       </c>
       <c r="R73" t="n">
-        <v>7365588</v>
+        <v>7365374</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8066,10 +8066,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117853209</v>
+        <v>117853197</v>
       </c>
       <c r="B74" t="n">
-        <v>91772</v>
+        <v>90650</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8078,25 +8078,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8106,10 +8106,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>822437</v>
+        <v>822876</v>
       </c>
       <c r="R74" t="n">
-        <v>7365878</v>
+        <v>7365854</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8168,10 +8168,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117853165</v>
+        <v>117853170</v>
       </c>
       <c r="B75" t="n">
-        <v>79069</v>
+        <v>56500</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8180,38 +8180,46 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>822653</v>
+        <v>822667</v>
       </c>
       <c r="R75" t="n">
-        <v>7365804</v>
+        <v>7365784</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8270,10 +8278,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117853197</v>
+        <v>117853192</v>
       </c>
       <c r="B76" t="n">
-        <v>90648</v>
+        <v>56492</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8282,25 +8290,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1503</v>
+        <v>102612</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8310,10 +8318,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>822876</v>
+        <v>822753</v>
       </c>
       <c r="R76" t="n">
-        <v>7365854</v>
+        <v>7365626</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8372,10 +8380,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117853177</v>
+        <v>117853175</v>
       </c>
       <c r="B77" t="n">
-        <v>56491</v>
+        <v>57441</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8388,34 +8396,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>822670</v>
+        <v>822405</v>
       </c>
       <c r="R77" t="n">
-        <v>7365699</v>
+        <v>7365900</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8474,10 +8490,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117853167</v>
+        <v>117853216</v>
       </c>
       <c r="B78" t="n">
-        <v>57287</v>
+        <v>91774</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8486,43 +8502,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>822380</v>
+        <v>823228</v>
       </c>
       <c r="R78" t="n">
-        <v>7365964</v>
+        <v>7365303</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8581,10 +8592,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117853184</v>
+        <v>117853193</v>
       </c>
       <c r="B79" t="n">
-        <v>78217</v>
+        <v>56492</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8597,21 +8608,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>102612</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8621,10 +8632,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>823212</v>
+        <v>822864</v>
       </c>
       <c r="R79" t="n">
-        <v>7365304</v>
+        <v>7365846</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8683,10 +8694,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117853178</v>
+        <v>117853177</v>
       </c>
       <c r="B80" t="n">
-        <v>79589</v>
+        <v>56492</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8695,25 +8706,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6461</v>
+        <v>102612</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8723,10 +8734,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>823075</v>
+        <v>822670</v>
       </c>
       <c r="R80" t="n">
-        <v>7365404</v>
+        <v>7365699</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8785,10 +8796,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117853170</v>
+        <v>117853184</v>
       </c>
       <c r="B81" t="n">
-        <v>56499</v>
+        <v>78219</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8797,46 +8808,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>822667</v>
+        <v>823212</v>
       </c>
       <c r="R81" t="n">
-        <v>7365784</v>
+        <v>7365304</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8895,10 +8898,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117853200</v>
+        <v>117853165</v>
       </c>
       <c r="B82" t="n">
-        <v>90648</v>
+        <v>79071</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8907,25 +8910,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8935,10 +8938,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>823068</v>
+        <v>822653</v>
       </c>
       <c r="R82" t="n">
-        <v>7365393</v>
+        <v>7365804</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -8997,10 +9000,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117853176</v>
+        <v>117853198</v>
       </c>
       <c r="B83" t="n">
-        <v>91815</v>
+        <v>90650</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9009,25 +9012,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5448</v>
+        <v>1503</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9037,10 +9040,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>823178</v>
+        <v>823072</v>
       </c>
       <c r="R83" t="n">
-        <v>7365412</v>
+        <v>7365396</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9099,10 +9102,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117853192</v>
+        <v>117853202</v>
       </c>
       <c r="B84" t="n">
-        <v>56491</v>
+        <v>90650</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9111,25 +9114,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102612</v>
+        <v>1503</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9139,10 +9142,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>822753</v>
+        <v>823210</v>
       </c>
       <c r="R84" t="n">
-        <v>7365626</v>
+        <v>7365304</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9201,10 +9204,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117853169</v>
+        <v>117853188</v>
       </c>
       <c r="B85" t="n">
-        <v>57287</v>
+        <v>78218</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9217,39 +9220,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>822940</v>
+        <v>822917</v>
       </c>
       <c r="R85" t="n">
-        <v>7365714</v>
+        <v>7365810</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9308,10 +9306,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117853219</v>
+        <v>117853163</v>
       </c>
       <c r="B86" t="n">
-        <v>91772</v>
+        <v>79100</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9320,25 +9318,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9348,10 +9346,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>822120</v>
+        <v>822961</v>
       </c>
       <c r="R86" t="n">
-        <v>7366257</v>
+        <v>7365570</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9410,10 +9408,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117853193</v>
+        <v>117853218</v>
       </c>
       <c r="B87" t="n">
-        <v>56491</v>
+        <v>91774</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9422,25 +9420,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9450,10 +9448,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>822864</v>
+        <v>823109</v>
       </c>
       <c r="R87" t="n">
-        <v>7365846</v>
+        <v>7365360</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9512,10 +9510,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117853180</v>
+        <v>117853200</v>
       </c>
       <c r="B88" t="n">
-        <v>91962</v>
+        <v>90650</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9524,25 +9522,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9552,10 +9550,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>822936</v>
+        <v>823068</v>
       </c>
       <c r="R88" t="n">
-        <v>7365718</v>
+        <v>7365393</v>
       </c>
       <c r="S88" t="n">
         <v>20</v>
@@ -9614,10 +9612,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117853183</v>
+        <v>117853161</v>
       </c>
       <c r="B89" t="n">
-        <v>91962</v>
+        <v>79100</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9630,21 +9628,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9654,10 +9652,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>823109</v>
+        <v>822791</v>
       </c>
       <c r="R89" t="n">
-        <v>7365464</v>
+        <v>7365910</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9716,10 +9714,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117853214</v>
+        <v>117853224</v>
       </c>
       <c r="B90" t="n">
-        <v>91772</v>
+        <v>78127</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9728,25 +9726,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9756,10 +9754,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>823096</v>
+        <v>822990</v>
       </c>
       <c r="R90" t="n">
-        <v>7365376</v>
+        <v>7365573</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -9818,10 +9816,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117853166</v>
+        <v>117853219</v>
       </c>
       <c r="B91" t="n">
-        <v>57287</v>
+        <v>91774</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9830,43 +9828,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>822278</v>
+        <v>822120</v>
       </c>
       <c r="R91" t="n">
-        <v>7366097</v>
+        <v>7366257</v>
       </c>
       <c r="S91" t="n">
         <v>20</v>
@@ -9925,10 +9918,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117853203</v>
+        <v>117853171</v>
       </c>
       <c r="B92" t="n">
-        <v>78480</v>
+        <v>56500</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9937,38 +9930,46 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>822790</v>
+        <v>822957</v>
       </c>
       <c r="R92" t="n">
-        <v>7365917</v>
+        <v>7365588</v>
       </c>
       <c r="S92" t="n">
         <v>20</v>
@@ -10027,10 +10028,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117853173</v>
+        <v>117853211</v>
       </c>
       <c r="B93" t="n">
-        <v>56499</v>
+        <v>91774</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10043,42 +10044,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>822971</v>
+        <v>822530</v>
       </c>
       <c r="R93" t="n">
-        <v>7365573</v>
+        <v>7365892</v>
       </c>
       <c r="S93" t="n">
         <v>20</v>
@@ -10137,10 +10130,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117853188</v>
+        <v>117853189</v>
       </c>
       <c r="B94" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10177,10 +10170,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>822917</v>
+        <v>823206</v>
       </c>
       <c r="R94" t="n">
-        <v>7365810</v>
+        <v>7365372</v>
       </c>
       <c r="S94" t="n">
         <v>20</v>
@@ -10239,10 +10232,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117853185</v>
+        <v>117853168</v>
       </c>
       <c r="B95" t="n">
-        <v>78217</v>
+        <v>57288</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10255,34 +10248,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>822091</v>
+        <v>822926</v>
       </c>
       <c r="R95" t="n">
-        <v>7366269</v>
+        <v>7365734</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -10341,10 +10339,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117853164</v>
+        <v>117853166</v>
       </c>
       <c r="B96" t="n">
-        <v>79069</v>
+        <v>57288</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10357,34 +10355,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>823236</v>
+        <v>822278</v>
       </c>
       <c r="R96" t="n">
-        <v>7365333</v>
+        <v>7366097</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -10443,10 +10446,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117853179</v>
+        <v>117853214</v>
       </c>
       <c r="B97" t="n">
-        <v>91962</v>
+        <v>91774</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10455,25 +10458,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10483,10 +10486,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>822868</v>
+        <v>823096</v>
       </c>
       <c r="R97" t="n">
-        <v>7365856</v>
+        <v>7365376</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10545,10 +10548,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117853216</v>
+        <v>117853183</v>
       </c>
       <c r="B98" t="n">
-        <v>91772</v>
+        <v>91964</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10557,25 +10560,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10585,10 +10588,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>823228</v>
+        <v>823109</v>
       </c>
       <c r="R98" t="n">
-        <v>7365303</v>
+        <v>7365464</v>
       </c>
       <c r="S98" t="n">
         <v>20</v>
@@ -10647,10 +10650,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117853163</v>
+        <v>117853164</v>
       </c>
       <c r="B99" t="n">
-        <v>79098</v>
+        <v>79071</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10663,21 +10666,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10687,10 +10690,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>822961</v>
+        <v>823236</v>
       </c>
       <c r="R99" t="n">
-        <v>7365570</v>
+        <v>7365333</v>
       </c>
       <c r="S99" t="n">
         <v>20</v>
@@ -10749,10 +10752,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117853161</v>
+        <v>117853194</v>
       </c>
       <c r="B100" t="n">
-        <v>79098</v>
+        <v>91964</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10765,21 +10768,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10789,10 +10792,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>822791</v>
+        <v>822973</v>
       </c>
       <c r="R100" t="n">
-        <v>7365910</v>
+        <v>7365566</v>
       </c>
       <c r="S100" t="n">
         <v>20</v>
@@ -10851,10 +10854,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>117853224</v>
+        <v>117853174</v>
       </c>
       <c r="B101" t="n">
-        <v>78125</v>
+        <v>56500</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10863,38 +10866,46 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>822990</v>
+        <v>822658</v>
       </c>
       <c r="R101" t="n">
-        <v>7365573</v>
+        <v>7365727</v>
       </c>
       <c r="S101" t="n">
         <v>20</v>
@@ -10953,10 +10964,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117853182</v>
+        <v>117853205</v>
       </c>
       <c r="B102" t="n">
-        <v>91962</v>
+        <v>78482</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10969,21 +10980,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10993,10 +11004,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>823221</v>
+        <v>823085</v>
       </c>
       <c r="R102" t="n">
-        <v>7365370</v>
+        <v>7365474</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -11055,10 +11066,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117853218</v>
+        <v>117853191</v>
       </c>
       <c r="B103" t="n">
-        <v>91772</v>
+        <v>56492</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11067,25 +11078,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11095,10 +11106,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>823109</v>
+        <v>822405</v>
       </c>
       <c r="R103" t="n">
-        <v>7365360</v>
+        <v>7365885</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -11157,10 +11168,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>117853211</v>
+        <v>117853207</v>
       </c>
       <c r="B104" t="n">
-        <v>91772</v>
+        <v>90745</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11169,25 +11180,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11197,10 +11208,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>822530</v>
+        <v>823183</v>
       </c>
       <c r="R104" t="n">
-        <v>7365892</v>
+        <v>7365421</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -11259,10 +11270,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>117853194</v>
+        <v>117853167</v>
       </c>
       <c r="B105" t="n">
-        <v>91962</v>
+        <v>57288</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11275,34 +11286,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>822973</v>
+        <v>822380</v>
       </c>
       <c r="R105" t="n">
-        <v>7365566</v>
+        <v>7365964</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -11361,10 +11377,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>117853174</v>
+        <v>117853190</v>
       </c>
       <c r="B106" t="n">
-        <v>56499</v>
+        <v>78218</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11373,46 +11389,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>822658</v>
+        <v>822973</v>
       </c>
       <c r="R106" t="n">
-        <v>7365727</v>
+        <v>7365570</v>
       </c>
       <c r="S106" t="n">
         <v>20</v>
@@ -11471,10 +11479,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>117853207</v>
+        <v>117853185</v>
       </c>
       <c r="B107" t="n">
-        <v>90743</v>
+        <v>78219</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11483,25 +11491,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11511,10 +11519,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>823183</v>
+        <v>822091</v>
       </c>
       <c r="R107" t="n">
-        <v>7365421</v>
+        <v>7366269</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -11573,10 +11581,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>117853175</v>
+        <v>117853213</v>
       </c>
       <c r="B108" t="n">
-        <v>57440</v>
+        <v>91774</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11585,46 +11593,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>822405</v>
+        <v>823075</v>
       </c>
       <c r="R108" t="n">
-        <v>7365900</v>
+        <v>7365464</v>
       </c>
       <c r="S108" t="n">
         <v>20</v>
@@ -11683,10 +11683,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>117853168</v>
+        <v>117853169</v>
       </c>
       <c r="B109" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11728,10 +11728,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>822926</v>
+        <v>822940</v>
       </c>
       <c r="R109" t="n">
-        <v>7365734</v>
+        <v>7365714</v>
       </c>
       <c r="S109" t="n">
         <v>20</v>
@@ -11790,10 +11790,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>117853202</v>
+        <v>117853179</v>
       </c>
       <c r="B110" t="n">
-        <v>90648</v>
+        <v>91964</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11802,25 +11802,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11830,10 +11830,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>823210</v>
+        <v>822868</v>
       </c>
       <c r="R110" t="n">
-        <v>7365304</v>
+        <v>7365856</v>
       </c>
       <c r="S110" t="n">
         <v>20</v>
@@ -11892,10 +11892,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>117853221</v>
+        <v>117853181</v>
       </c>
       <c r="B111" t="n">
-        <v>91772</v>
+        <v>91964</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11904,25 +11904,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11932,10 +11932,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>822747</v>
+        <v>822952</v>
       </c>
       <c r="R111" t="n">
-        <v>7365610</v>
+        <v>7365646</v>
       </c>
       <c r="S111" t="n">
         <v>20</v>
@@ -11994,10 +11994,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>117853190</v>
+        <v>117853209</v>
       </c>
       <c r="B112" t="n">
-        <v>78216</v>
+        <v>91774</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12006,25 +12006,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12034,10 +12034,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>822973</v>
+        <v>822437</v>
       </c>
       <c r="R112" t="n">
-        <v>7365570</v>
+        <v>7365878</v>
       </c>
       <c r="S112" t="n">
         <v>20</v>

--- a/artfynd/A 46558-2023 artfynd.xlsx
+++ b/artfynd/A 46558-2023 artfynd.xlsx
@@ -11270,10 +11270,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>117853167</v>
+        <v>117853190</v>
       </c>
       <c r="B105" t="n">
-        <v>57288</v>
+        <v>78218</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11286,39 +11286,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>822380</v>
+        <v>822973</v>
       </c>
       <c r="R105" t="n">
-        <v>7365964</v>
+        <v>7365570</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -11377,10 +11372,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>117853190</v>
+        <v>117853167</v>
       </c>
       <c r="B106" t="n">
-        <v>78218</v>
+        <v>57288</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11393,34 +11388,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kesas-Dalheden, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>822973</v>
+        <v>822380</v>
       </c>
       <c r="R106" t="n">
-        <v>7365570</v>
+        <v>7365964</v>
       </c>
       <c r="S106" t="n">
         <v>20</v>

--- a/artfynd/A 46558-2023 artfynd.xlsx
+++ b/artfynd/A 46558-2023 artfynd.xlsx
@@ -7862,11 +7862,11 @@
         <v>117853173</v>
       </c>
       <c r="B72" t="n">
-        <v>56502</v>
+        <v>56593</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9405,11 +9405,11 @@
         <v>117853172</v>
       </c>
       <c r="B87" t="n">
-        <v>56502</v>
+        <v>56593</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10545,11 +10545,11 @@
         <v>117853174</v>
       </c>
       <c r="B98" t="n">
-        <v>56502</v>
+        <v>56593</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -11267,11 +11267,11 @@
         <v>117853170</v>
       </c>
       <c r="B105" t="n">
-        <v>56502</v>
+        <v>56593</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11377,11 +11377,11 @@
         <v>117853171</v>
       </c>
       <c r="B106" t="n">
-        <v>56502</v>
+        <v>56593</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">

--- a/artfynd/A 46558-2023 artfynd.xlsx
+++ b/artfynd/A 46558-2023 artfynd.xlsx
@@ -7862,11 +7862,11 @@
         <v>117853173</v>
       </c>
       <c r="B72" t="n">
-        <v>56593</v>
+        <v>56502</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9405,11 +9405,11 @@
         <v>117853172</v>
       </c>
       <c r="B87" t="n">
-        <v>56593</v>
+        <v>56502</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10545,11 +10545,11 @@
         <v>117853174</v>
       </c>
       <c r="B98" t="n">
-        <v>56593</v>
+        <v>56502</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -11267,11 +11267,11 @@
         <v>117853170</v>
       </c>
       <c r="B105" t="n">
-        <v>56593</v>
+        <v>56502</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11377,11 +11377,11 @@
         <v>117853171</v>
       </c>
       <c r="B106" t="n">
-        <v>56593</v>
+        <v>56502</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
